--- a/candat_data.xlsx
+++ b/candat_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OUT247277\Desktop\Cand Tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\out299053\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE6EE1A-65F3-494D-B602-19027BFD36FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AD0496-A4F9-48B0-9476-4E735F0584E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chatting &amp; Idle" sheetId="1" r:id="rId1"/>
@@ -2521,10 +2521,6 @@
   </si>
   <si>
     <t>اهلا بحضرتك اتمنالك يوم سعيد 🤩 بنعتذر جدا عن وقت الانتظار ⏱️
-استفسار حضرتك علي رقم xxxx ؟ بخصوص xxxx ؟</t>
-  </si>
-  <si>
-    <t>اهلا بحضرتك اتمنالك يوم سعيد 🤩 بنعتذر جدا عن وقت الانتظار ⏱️
 ممكن توضيح استفسار حضرتك بخصوص الرقم xxxxx ؟</t>
   </si>
   <si>
@@ -4503,6 +4499,10 @@
   </si>
   <si>
     <t>تصعيد FTTH Physical</t>
+  </si>
+  <si>
+    <t>اهلا بحضرتك اتمنالك يوم سعيد 🤩 بنعتذر جدا عن وقت الانتظار ⏱️
+استفسار حضرتك علي رقم xxxxx ؟ بخصوص xxxxx ؟</t>
   </si>
 </sst>
 </file>
@@ -5024,10 +5024,10 @@
     </row>
     <row r="2" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>582</v>
+        <v>952</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -5041,7 +5041,7 @@
         <v>567</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -5049,7 +5049,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -5063,7 +5063,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
@@ -5105,7 +5105,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -5119,7 +5119,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -5133,7 +5133,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -5147,7 +5147,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -5257,82 +5257,82 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B7" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B8" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B9" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B10" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B11" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
   </sheetData>
@@ -5365,7 +5365,7 @@
         <v>298</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="3" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>542</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="110.25" x14ac:dyDescent="0.25">
@@ -5395,47 +5395,47 @@
         <v>543</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5490,74 +5490,74 @@
     </row>
     <row r="2" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>600</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>602</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>604</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>606</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>608</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>610</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>612</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>614</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>616</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
@@ -5565,79 +5565,79 @@
         <v>71</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="135" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>619</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>621</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="189" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>623</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="189" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>625</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>627</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="299.25" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>629</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="378" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
+        <v>630</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>631</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
+        <v>632</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>633</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="150" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
+        <v>634</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>635</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -5666,130 +5666,130 @@
     </row>
     <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>640</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>642</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>644</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>646</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>648</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="315" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>650</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="315" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>652</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>654</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>657</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>659</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>661</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>663</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>665</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>667</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -5797,23 +5797,23 @@
         <v>122</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>670</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>672</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -5986,7 +5986,7 @@
         <v>309</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -6000,7 +6000,7 @@
         <v>310</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -6014,7 +6014,7 @@
         <v>430</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -6028,7 +6028,7 @@
         <v>311</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -6042,7 +6042,7 @@
         <v>312</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -6056,55 +6056,55 @@
         <v>570</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>679</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="189" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -6323,7 +6323,7 @@
         <v>331</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -6334,7 +6334,7 @@
     </row>
     <row r="3" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>328</v>
@@ -6348,7 +6348,7 @@
     </row>
     <row r="4" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>330</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="5" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>329</v>
@@ -6733,7 +6733,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -6747,7 +6747,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -6758,10 +6758,10 @@
     </row>
     <row r="4" spans="1:4" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="110.25" x14ac:dyDescent="0.25">
@@ -6769,7 +6769,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -6783,7 +6783,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -6797,7 +6797,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -6811,7 +6811,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -6825,7 +6825,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -6881,7 +6881,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -6979,7 +6979,7 @@
         <v>555</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C20" t="s">
         <v>6</v>
@@ -7043,7 +7043,7 @@
         <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
@@ -7379,7 +7379,7 @@
         <v>72</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C49" t="s">
         <v>6</v>
@@ -7393,7 +7393,7 @@
         <v>73</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C50" t="s">
         <v>6</v>
@@ -7407,7 +7407,7 @@
         <v>74</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C51" t="s">
         <v>6</v>
@@ -7421,7 +7421,7 @@
         <v>75</v>
       </c>
       <c r="B52" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C52" t="s">
         <v>6</v>
@@ -7449,7 +7449,7 @@
         <v>76</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C54" t="s">
         <v>6</v>
@@ -7463,7 +7463,7 @@
         <v>77</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C55" t="s">
         <v>6</v>
@@ -7491,63 +7491,63 @@
         <v>523</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>857</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>858</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
   </sheetData>
@@ -9023,15 +9023,15 @@
     </row>
     <row r="6" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>948</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B7" t="s">
         <v>443</v>
@@ -9045,10 +9045,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B8" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -9648,7 +9648,7 @@
         <v>149</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -9662,7 +9662,7 @@
         <v>150</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -9774,7 +9774,7 @@
         <v>160</v>
       </c>
       <c r="B12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -9816,7 +9816,7 @@
         <v>164</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -9872,7 +9872,7 @@
         <v>170</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
@@ -9998,7 +9998,7 @@
         <v>182</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C28" t="s">
         <v>6</v>
@@ -10054,7 +10054,7 @@
         <v>183</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C32" t="s">
         <v>6</v>
@@ -10124,7 +10124,7 @@
         <v>191</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C37" t="s">
         <v>6</v>
@@ -10166,7 +10166,7 @@
         <v>194</v>
       </c>
       <c r="B40" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C40" t="s">
         <v>6</v>
@@ -10180,7 +10180,7 @@
         <v>72</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C41" t="s">
         <v>6</v>
@@ -10208,7 +10208,7 @@
         <v>197</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C43" t="s">
         <v>6</v>
@@ -10300,7 +10300,7 @@
         <v>205</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C50" t="s">
         <v>6</v>
@@ -10314,7 +10314,7 @@
         <v>206</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C51" t="s">
         <v>6</v>
@@ -10412,7 +10412,7 @@
         <v>216</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C58" t="s">
         <v>6</v>
@@ -10440,7 +10440,7 @@
         <v>524</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C60" t="s">
         <v>6</v>
@@ -10451,34 +10451,34 @@
     </row>
     <row r="61" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
@@ -10486,7 +10486,7 @@
         <v>218</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C65" t="s">
         <v>6</v>
@@ -10497,10 +10497,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B66" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C66" t="s">
         <v>6</v>
@@ -10511,10 +10511,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B67" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C67" t="s">
         <v>6</v>
@@ -10525,10 +10525,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B68" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C68" t="s">
         <v>6</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B69" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C69" t="s">
         <v>6</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B70" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C70" t="s">
         <v>6</v>
@@ -10567,10 +10567,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B71" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C71" t="s">
         <v>6</v>
@@ -10581,10 +10581,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B72" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C72" t="s">
         <v>6</v>
@@ -10612,7 +10612,7 @@
         <v>221</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C74" t="s">
         <v>6</v>
@@ -10626,7 +10626,7 @@
         <v>222</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C75" t="s">
         <v>6</v>
@@ -10640,7 +10640,7 @@
         <v>223</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C76" t="s">
         <v>6</v>
@@ -10696,7 +10696,7 @@
         <v>229</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C80" t="s">
         <v>6</v>
@@ -10707,58 +10707,58 @@
     </row>
     <row r="81" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="126" x14ac:dyDescent="0.25">
@@ -10766,7 +10766,7 @@
         <v>230</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C88" t="s">
         <v>6</v>
@@ -10780,7 +10780,7 @@
         <v>231</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C89" t="s">
         <v>6</v>
@@ -10808,7 +10808,7 @@
         <v>234</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C91" t="s">
         <v>6</v>
@@ -10822,7 +10822,7 @@
         <v>235</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C92" t="s">
         <v>6</v>
@@ -10864,7 +10864,7 @@
         <v>525</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C95" t="s">
         <v>6</v>
@@ -10875,34 +10875,34 @@
     </row>
     <row r="96" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="63" x14ac:dyDescent="0.25">
@@ -10910,7 +10910,7 @@
         <v>526</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C100" t="s">
         <v>6</v>
@@ -10921,26 +10921,26 @@
     </row>
     <row r="101" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C103" t="s">
         <v>6</v>
@@ -10951,10 +10951,10 @@
     </row>
     <row r="104" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C104" t="s">
         <v>6</v>
@@ -10968,7 +10968,7 @@
         <v>240</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C105" t="s">
         <v>6</v>
@@ -11014,7 +11014,7 @@
         <v>241</v>
       </c>
       <c r="B2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -11028,7 +11028,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -11039,10 +11039,10 @@
     </row>
     <row r="4" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -11053,10 +11053,10 @@
     </row>
     <row r="5" spans="1:4" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -11067,10 +11067,10 @@
     </row>
     <row r="6" spans="1:4" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -11081,10 +11081,10 @@
     </row>
     <row r="7" spans="1:4" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -11095,10 +11095,10 @@
     </row>
     <row r="8" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -11109,10 +11109,10 @@
     </row>
     <row r="9" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -11123,10 +11123,10 @@
     </row>
     <row r="10" spans="1:4" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -11137,10 +11137,10 @@
     </row>
     <row r="11" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -11151,10 +11151,10 @@
     </row>
     <row r="12" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -11165,10 +11165,10 @@
     </row>
     <row r="13" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -11179,10 +11179,10 @@
     </row>
     <row r="14" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -11193,10 +11193,10 @@
     </row>
     <row r="15" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -11210,7 +11210,7 @@
         <v>242</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
@@ -11224,7 +11224,7 @@
         <v>243</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
@@ -11235,10 +11235,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
@@ -11249,10 +11249,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B19" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
@@ -11263,10 +11263,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B20" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C20" t="s">
         <v>6</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B21" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
@@ -11291,10 +11291,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B22" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C22" t="s">
         <v>6</v>
@@ -11305,10 +11305,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B23" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
@@ -11319,10 +11319,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B24" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C24" t="s">
         <v>6</v>
@@ -11336,7 +11336,7 @@
         <v>244</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
@@ -11350,7 +11350,7 @@
         <v>72</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C26" t="s">
         <v>6</v>
@@ -11392,7 +11392,7 @@
         <v>245</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C29" t="s">
         <v>6</v>
@@ -11490,7 +11490,7 @@
         <v>251</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
@@ -11630,7 +11630,7 @@
         <v>261</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C46" t="s">
         <v>6</v>
@@ -11644,7 +11644,7 @@
         <v>262</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C47" t="s">
         <v>6</v>
@@ -11669,10 +11669,10 @@
     </row>
     <row r="49" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>595</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="110.25" x14ac:dyDescent="0.25">
@@ -11680,7 +11680,7 @@
         <v>264</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C50" t="s">
         <v>6</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="53" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>735</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>736</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>737</v>
       </c>
       <c r="C53" t="s">
         <v>6</v>
@@ -11736,7 +11736,7 @@
         <v>416</v>
       </c>
       <c r="B54" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C54" t="s">
         <v>6</v>
@@ -11793,7 +11793,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>581</v>
@@ -11801,34 +11801,34 @@
     </row>
     <row r="4" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -11836,7 +11836,7 @@
         <v>268</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -11850,7 +11850,7 @@
         <v>269</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -11864,7 +11864,7 @@
         <v>270</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -11892,7 +11892,7 @@
         <v>272</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -11934,7 +11934,7 @@
         <v>275</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -11948,7 +11948,7 @@
         <v>276</v>
       </c>
       <c r="B16" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
@@ -12018,7 +12018,7 @@
         <v>283</v>
       </c>
       <c r="B21" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
@@ -12046,7 +12046,7 @@
         <v>285</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
@@ -12071,18 +12071,18 @@
     </row>
     <row r="25" spans="1:4" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -12121,7 +12121,7 @@
         <v>579</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
@@ -12175,7 +12175,7 @@
         <v>289</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -12200,10 +12200,10 @@
     </row>
     <row r="10" spans="1:4" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -12217,7 +12217,7 @@
         <v>554</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -12309,7 +12309,7 @@
         <v>297</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
@@ -12378,82 +12378,82 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B5" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -12484,90 +12484,90 @@
     </row>
     <row r="2" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="126" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
   </sheetData>

--- a/candat_data.xlsx
+++ b/candat_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\out299053\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AD0496-A4F9-48B0-9476-4E735F0584E8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8F701A-C330-4788-A42A-5913559E1DE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chatting &amp; Idle" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="953">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="959">
   <si>
     <t>Name</t>
   </si>
@@ -4503,6 +4503,24 @@
   <si>
     <t>اهلا بحضرتك اتمنالك يوم سعيد 🤩 بنعتذر جدا عن وقت الانتظار ⏱️
 استفسار حضرتك علي رقم xxxxx ؟ بخصوص xxxxx ؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تم تسجيل العطل الفني الخاص بحضرتك، وهيتم التواصل معاك في أقرب وقت. مش هتحتاج تعمل أي خطوات فنية، لأن السيستم هيقوم بتنفيذ الخطوات المطلوبة تلقائيًا، وده هيساعدنا نتعامل مع المشكلة بشكل أسرع و رقم الشكوي </t>
+  </si>
+  <si>
+    <t>Automation Script</t>
+  </si>
+  <si>
+    <t>Automation DataDown</t>
+  </si>
+  <si>
+    <t>Automation Instability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pop outage checked, Check TTS History before starting troubleshooting, whatever the ticket open or closed : No ticket, BSS history Checked:, Check FBB Account Status on BSS : Active, Check FBB Package Status on BSS : Active, Line Status : Enabled, Is The Line TDM ?, No, Check FV status on CST360 from FV profile from Port details, Used, Check customer subscription : Normal customer / Indigo, Check if customer has Voice Overlapping : No, Internet Not working, Router ADSL LED (VS) ( [ CST360 ]/[ Matrix for TDM ] ) Status : Both Down, Is there an open physical ticket on TTs, No, Check if CPE is connected from main, Yes, Check voice status ?, Working / Not Sure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pop outage checked, Check TTS History before starting troubleshooting, whatever the ticket open or closed : No ticket, BSS history Checked:, Check FBB Account Status on BSS : Active, Check FBB Package Status on BSS : Active, Line Status : Enabled, Is The Line TDM ?, No, Check FV status on CST360 from FV profile from Port details, Used, Check customer subscription : Normal customer / Indigo, Check if customer has Voice Overlapping : No, Line working but unstable, Is there an open physical ticket on TTs, No, Check if CPE is connected from main, Yes, Check voice status ?, Voice working/Not sure </t>
   </si>
 </sst>
 </file>
@@ -8947,7 +8965,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.625" customWidth="1"/>
@@ -9595,6 +9613,30 @@
       </c>
       <c r="D47">
         <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>954</v>
+      </c>
+      <c r="B48" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>955</v>
+      </c>
+      <c r="B49" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>956</v>
+      </c>
+      <c r="B50" t="s">
+        <v>958</v>
       </c>
     </row>
   </sheetData>
